--- a/mockups/site-brief/review/sitenalyzer-synthetic-research-dictionary.xlsx
+++ b/mockups/site-brief/review/sitenalyzer-synthetic-research-dictionary.xlsx
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0">Export_Info!$A$1:$B$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1">Sources!$A$1:$Q$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2">Assets!$A$1:$U$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2">Assets!$A$1:$U$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3">Fields!$A$1:$AH$64</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4">Value_Sets!$A$1:$K$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5">Relationships!$A$1:$J$2</definedName>
@@ -647,7 +647,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U9"/>
+  <dimension ref="A1:U10"/>
   <cols>
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
     <col min="2" max="2" width="28.83203125" customWidth="1"/>
@@ -1257,10 +1257,75 @@
         <v/>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>00000000-0000-4000-8000-000000000001_termstore</v>
+      </c>
+      <c r="B10" t="str">
+        <v>00000000-0000-4000-8000-000000000001</v>
+      </c>
+      <c r="C10" t="str">
+        <v>TermStore</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Term Store</v>
+      </c>
+      <c r="E10" t="str">
+        <v>SharePoint Term Store</v>
+      </c>
+      <c r="F10" t="str">
+        <v>https://example.sharepoint.com/sites/research-example/_layouts/15/termstoremanager.aspx</v>
+      </c>
+      <c r="G10" t="str">
+        <v>https://example.sharepoint.com/sites/research-example</v>
+      </c>
+      <c r="H10" t="str">
+        <v>https://example.sharepoint.com/sites/research-example</v>
+      </c>
+      <c r="I10" t="str">
+        <v>SharePoint Managed Metadata term store</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v/>
+      </c>
+      <c r="M10" t="str">
+        <v>Source</v>
+      </c>
+      <c r="N10" t="str">
+        <v>Real-time</v>
+      </c>
+      <c r="O10" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="P10" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="Q10" t="str">
+        <v/>
+      </c>
+      <c r="R10" t="str">
+        <v/>
+      </c>
+      <c r="S10" t="str">
+        <v>owner@example.org</v>
+      </c>
+      <c r="T10" t="str">
+        <v>Active</v>
+      </c>
+      <c r="U10" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:U9"/>
+  <autoFilter ref="A1:U10"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:U9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:U10"/>
   </ignoredErrors>
 </worksheet>
 </file>
